--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2025/202510/AllSymbols_P&L_20251023.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2025/202510/AllSymbols_P&L_20251023.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="167">
   <si>
     <t>Symbol</t>
   </si>
@@ -124,6 +124,9 @@
     <t>DFDV</t>
   </si>
   <si>
+    <t>DFDVW</t>
+  </si>
+  <si>
     <t>DG</t>
   </si>
   <si>
@@ -485,9 +488,6 @@
   </si>
   <si>
     <t>VST 21JAN28 320 C</t>
-  </si>
-  <si>
-    <t>DFDVW</t>
   </si>
   <si>
     <t>HKD</t>
@@ -2243,16 +2243,16 @@
         <v>36</v>
       </c>
       <c r="B48">
-        <v>16231</v>
+        <v>63</v>
       </c>
       <c r="C48">
-        <v>102.99</v>
+        <v>0.0137</v>
       </c>
       <c r="D48">
-        <v>-9576.290000000001</v>
+        <v>-0</v>
       </c>
       <c r="E48">
-        <v>1671630.69</v>
+        <v>0.86</v>
       </c>
       <c r="F48" t="s">
         <v>161</v>
@@ -2264,7 +2264,7 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>1671630.69</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2272,16 +2272,16 @@
         <v>37</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>16231</v>
       </c>
       <c r="C49">
-        <v>94.89</v>
+        <v>102.99</v>
       </c>
       <c r="D49">
-        <v>1.76</v>
+        <v>-9576.290000000001</v>
       </c>
       <c r="E49">
-        <v>379.56</v>
+        <v>1671630.69</v>
       </c>
       <c r="F49" t="s">
         <v>161</v>
@@ -2293,7 +2293,7 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>379.56</v>
+        <v>1671630.69</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2301,16 +2301,16 @@
         <v>38</v>
       </c>
       <c r="B50">
-        <v>1815</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>133.19</v>
+        <v>94.89</v>
       </c>
       <c r="D50">
-        <v>5590.2</v>
+        <v>1.76</v>
       </c>
       <c r="E50">
-        <v>241739.85</v>
+        <v>379.56</v>
       </c>
       <c r="F50" t="s">
         <v>161</v>
@@ -2322,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>241739.85</v>
+        <v>379.56</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2330,16 +2330,16 @@
         <v>39</v>
       </c>
       <c r="B51">
-        <v>843</v>
+        <v>1815</v>
       </c>
       <c r="C51">
-        <v>372.4</v>
+        <v>133.19</v>
       </c>
       <c r="D51">
-        <v>9947.4</v>
+        <v>5590.2</v>
       </c>
       <c r="E51">
-        <v>313933.2</v>
+        <v>241739.85</v>
       </c>
       <c r="F51" t="s">
         <v>161</v>
@@ -2351,7 +2351,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>313933.2</v>
+        <v>241739.85</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2359,16 +2359,16 @@
         <v>40</v>
       </c>
       <c r="B52">
-        <v>-303000</v>
+        <v>843</v>
       </c>
       <c r="C52">
-        <v>33.38</v>
+        <v>372.4</v>
       </c>
       <c r="D52">
-        <v>-45450</v>
+        <v>9947.4</v>
       </c>
       <c r="E52">
-        <v>-10114140</v>
+        <v>313933.2</v>
       </c>
       <c r="F52" t="s">
         <v>161</v>
@@ -2380,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>-10114140</v>
+        <v>313933.2</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2388,16 +2388,16 @@
         <v>41</v>
       </c>
       <c r="B53">
-        <v>8473</v>
+        <v>-303000</v>
       </c>
       <c r="C53">
-        <v>66.02</v>
+        <v>33.38</v>
       </c>
       <c r="D53">
-        <v>4321.23</v>
+        <v>-45450</v>
       </c>
       <c r="E53">
-        <v>559387.46</v>
+        <v>-10114140</v>
       </c>
       <c r="F53" t="s">
         <v>161</v>
@@ -2409,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>559387.46</v>
+        <v>-10114140</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2417,16 +2417,16 @@
         <v>42</v>
       </c>
       <c r="B54">
-        <v>8</v>
+        <v>8473</v>
       </c>
       <c r="C54">
-        <v>30.47</v>
+        <v>66.02</v>
       </c>
       <c r="D54">
-        <v>3.52</v>
+        <v>4321.23</v>
       </c>
       <c r="E54">
-        <v>243.76</v>
+        <v>559387.46</v>
       </c>
       <c r="F54" t="s">
         <v>161</v>
@@ -2438,7 +2438,7 @@
         <v>1</v>
       </c>
       <c r="I54">
-        <v>243.76</v>
+        <v>559387.46</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2446,16 +2446,16 @@
         <v>43</v>
       </c>
       <c r="B55">
-        <v>3285</v>
+        <v>8</v>
       </c>
       <c r="C55">
-        <v>306.39</v>
+        <v>30.47</v>
       </c>
       <c r="D55">
-        <v>27922.5</v>
+        <v>3.52</v>
       </c>
       <c r="E55">
-        <v>1006491.15</v>
+        <v>243.76</v>
       </c>
       <c r="F55" t="s">
         <v>161</v>
@@ -2467,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="I55">
-        <v>1006491.15</v>
+        <v>243.76</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2475,16 +2475,16 @@
         <v>44</v>
       </c>
       <c r="B56">
-        <v>75</v>
+        <v>3285</v>
       </c>
       <c r="C56">
-        <v>595.15</v>
+        <v>306.39</v>
       </c>
       <c r="D56">
-        <v>1436.25</v>
+        <v>27922.5</v>
       </c>
       <c r="E56">
-        <v>44636.25</v>
+        <v>1006491.15</v>
       </c>
       <c r="F56" t="s">
         <v>161</v>
@@ -2496,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>44636.25</v>
+        <v>1006491.15</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2504,16 +2504,16 @@
         <v>45</v>
       </c>
       <c r="B57">
-        <v>6800</v>
+        <v>75</v>
       </c>
       <c r="C57">
-        <v>750.78</v>
+        <v>595.15</v>
       </c>
       <c r="D57">
-        <v>42024</v>
+        <v>1436.25</v>
       </c>
       <c r="E57">
-        <v>5105304</v>
+        <v>44636.25</v>
       </c>
       <c r="F57" t="s">
         <v>161</v>
@@ -2525,7 +2525,7 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>5105304</v>
+        <v>44636.25</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2533,16 +2533,16 @@
         <v>46</v>
       </c>
       <c r="B58">
-        <v>75</v>
+        <v>6800</v>
       </c>
       <c r="C58">
-        <v>385.03</v>
+        <v>750.78</v>
       </c>
       <c r="D58">
-        <v>-295.5</v>
+        <v>42024</v>
       </c>
       <c r="E58">
-        <v>28877.25</v>
+        <v>5105304</v>
       </c>
       <c r="F58" t="s">
         <v>161</v>
@@ -2554,7 +2554,7 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>28877.25</v>
+        <v>5105304</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2562,16 +2562,16 @@
         <v>47</v>
       </c>
       <c r="B59">
-        <v>375</v>
+        <v>75</v>
       </c>
       <c r="C59">
-        <v>285</v>
+        <v>385.03</v>
       </c>
       <c r="D59">
-        <v>-941.25</v>
+        <v>-295.5</v>
       </c>
       <c r="E59">
-        <v>106875</v>
+        <v>28877.25</v>
       </c>
       <c r="F59" t="s">
         <v>161</v>
@@ -2583,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="I59">
-        <v>106875</v>
+        <v>28877.25</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2591,16 +2591,16 @@
         <v>48</v>
       </c>
       <c r="B60">
-        <v>2122</v>
+        <v>375</v>
       </c>
       <c r="C60">
-        <v>157.45</v>
+        <v>285</v>
       </c>
       <c r="D60">
-        <v>1061</v>
+        <v>-941.25</v>
       </c>
       <c r="E60">
-        <v>334108.9</v>
+        <v>106875</v>
       </c>
       <c r="F60" t="s">
         <v>161</v>
@@ -2612,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>334108.9</v>
+        <v>106875</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2620,16 +2620,16 @@
         <v>49</v>
       </c>
       <c r="B61">
-        <v>47997</v>
+        <v>2122</v>
       </c>
       <c r="C61">
-        <v>53.27</v>
+        <v>157.45</v>
       </c>
       <c r="D61">
-        <v>18238.86</v>
+        <v>1061</v>
       </c>
       <c r="E61">
-        <v>2556800.19</v>
+        <v>334108.9</v>
       </c>
       <c r="F61" t="s">
         <v>161</v>
@@ -2641,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="I61">
-        <v>2556800.19</v>
+        <v>334108.9</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2649,16 +2649,16 @@
         <v>50</v>
       </c>
       <c r="B62">
-        <v>19000</v>
+        <v>47997</v>
       </c>
       <c r="C62">
-        <v>294.54</v>
+        <v>53.27</v>
       </c>
       <c r="D62">
-        <v>8170</v>
+        <v>18238.86</v>
       </c>
       <c r="E62">
-        <v>5596260</v>
+        <v>2556800.19</v>
       </c>
       <c r="F62" t="s">
         <v>161</v>
@@ -2670,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="I62">
-        <v>5596260</v>
+        <v>2556800.19</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2678,16 +2678,16 @@
         <v>51</v>
       </c>
       <c r="B63">
-        <v>29646</v>
+        <v>19000</v>
       </c>
       <c r="C63">
-        <v>60.18</v>
+        <v>294.54</v>
       </c>
       <c r="D63">
-        <v>-7707.96</v>
+        <v>8170</v>
       </c>
       <c r="E63">
-        <v>1784096.28</v>
+        <v>5596260</v>
       </c>
       <c r="F63" t="s">
         <v>161</v>
@@ -2699,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>1784096.28</v>
+        <v>5596260</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2707,16 +2707,16 @@
         <v>52</v>
       </c>
       <c r="B64">
-        <v>9760</v>
+        <v>29646</v>
       </c>
       <c r="C64">
-        <v>6.48</v>
+        <v>60.18</v>
       </c>
       <c r="D64">
-        <v>-2049.6</v>
+        <v>-7707.96</v>
       </c>
       <c r="E64">
-        <v>63244.8</v>
+        <v>1784096.28</v>
       </c>
       <c r="F64" t="s">
         <v>161</v>
@@ -2728,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <v>63244.8</v>
+        <v>1784096.28</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2736,16 +2736,16 @@
         <v>53</v>
       </c>
       <c r="B65">
-        <v>750</v>
+        <v>9760</v>
       </c>
       <c r="C65">
-        <v>821.04</v>
+        <v>6.48</v>
       </c>
       <c r="D65">
-        <v>6457.5</v>
+        <v>-2049.6</v>
       </c>
       <c r="E65">
-        <v>615780</v>
+        <v>63244.8</v>
       </c>
       <c r="F65" t="s">
         <v>161</v>
@@ -2757,7 +2757,7 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>615780</v>
+        <v>63244.8</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2765,28 +2765,28 @@
         <v>54</v>
       </c>
       <c r="B66">
-        <v>4225800</v>
+        <v>750</v>
       </c>
       <c r="C66">
-        <v>2.18</v>
+        <v>821.04</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>6457.5</v>
       </c>
       <c r="E66">
-        <v>9212244</v>
+        <v>615780</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
         <v>162</v>
       </c>
       <c r="H66">
-        <v>0.7702</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>7095270.33</v>
+        <v>615780</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2794,28 +2794,28 @@
         <v>55</v>
       </c>
       <c r="B67">
-        <v>76</v>
+        <v>4225800</v>
       </c>
       <c r="C67">
-        <v>2148.32</v>
+        <v>2.18</v>
       </c>
       <c r="D67">
-        <v>4036.36</v>
+        <v>0</v>
       </c>
       <c r="E67">
-        <v>163272.32</v>
+        <v>9212244</v>
       </c>
       <c r="F67" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G67" t="s">
         <v>162</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>0.7702</v>
       </c>
       <c r="I67">
-        <v>163272.32</v>
+        <v>7095270.33</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2823,16 +2823,16 @@
         <v>56</v>
       </c>
       <c r="B68">
-        <v>9000</v>
+        <v>76</v>
       </c>
       <c r="C68">
-        <v>68.45</v>
+        <v>2148.32</v>
       </c>
       <c r="D68">
-        <v>-12150</v>
+        <v>4036.36</v>
       </c>
       <c r="E68">
-        <v>616050</v>
+        <v>163272.32</v>
       </c>
       <c r="F68" t="s">
         <v>161</v>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <v>616050</v>
+        <v>163272.32</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2852,16 +2852,16 @@
         <v>57</v>
       </c>
       <c r="B69">
-        <v>15590</v>
+        <v>9000</v>
       </c>
       <c r="C69">
-        <v>88.81999999999999</v>
+        <v>68.45</v>
       </c>
       <c r="D69">
-        <v>21826</v>
+        <v>-12150</v>
       </c>
       <c r="E69">
-        <v>1384703.8</v>
+        <v>616050</v>
       </c>
       <c r="F69" t="s">
         <v>161</v>
@@ -2873,7 +2873,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>1384703.8</v>
+        <v>616050</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2881,16 +2881,16 @@
         <v>58</v>
       </c>
       <c r="B70">
-        <v>1363</v>
+        <v>15590</v>
       </c>
       <c r="C70">
-        <v>605.74</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="D70">
-        <v>12621.38</v>
+        <v>21826</v>
       </c>
       <c r="E70">
-        <v>825623.62</v>
+        <v>1384703.8</v>
       </c>
       <c r="F70" t="s">
         <v>161</v>
@@ -2902,7 +2902,7 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <v>825623.62</v>
+        <v>1384703.8</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2910,16 +2910,16 @@
         <v>59</v>
       </c>
       <c r="B71">
-        <v>7</v>
+        <v>1363</v>
       </c>
       <c r="C71">
-        <v>939.17</v>
+        <v>605.74</v>
       </c>
       <c r="D71">
-        <v>24.64</v>
+        <v>12621.38</v>
       </c>
       <c r="E71">
-        <v>6574.19</v>
+        <v>825623.62</v>
       </c>
       <c r="F71" t="s">
         <v>161</v>
@@ -2931,7 +2931,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>6574.19</v>
+        <v>825623.62</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2939,16 +2939,16 @@
         <v>60</v>
       </c>
       <c r="B72">
-        <v>813200</v>
+        <v>7</v>
       </c>
       <c r="C72">
-        <v>1.02</v>
+        <v>939.17</v>
       </c>
       <c r="D72">
-        <v>-8132</v>
+        <v>24.64</v>
       </c>
       <c r="E72">
-        <v>829464</v>
+        <v>6574.19</v>
       </c>
       <c r="F72" t="s">
         <v>161</v>
@@ -2960,7 +2960,7 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>829464</v>
+        <v>6574.19</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -2968,16 +2968,16 @@
         <v>61</v>
       </c>
       <c r="B73">
-        <v>1150</v>
+        <v>813200</v>
       </c>
       <c r="C73">
-        <v>182.16</v>
+        <v>1.02</v>
       </c>
       <c r="D73">
-        <v>2162</v>
+        <v>-8132</v>
       </c>
       <c r="E73">
-        <v>209484</v>
+        <v>829464</v>
       </c>
       <c r="F73" t="s">
         <v>161</v>
@@ -2989,7 +2989,7 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <v>209484</v>
+        <v>829464</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -2997,16 +2997,16 @@
         <v>62</v>
       </c>
       <c r="B74">
-        <v>25486</v>
+        <v>1150</v>
       </c>
       <c r="C74">
-        <v>60.22</v>
+        <v>182.16</v>
       </c>
       <c r="D74">
-        <v>-1274.3</v>
+        <v>2162</v>
       </c>
       <c r="E74">
-        <v>1534766.92</v>
+        <v>209484</v>
       </c>
       <c r="F74" t="s">
         <v>161</v>
@@ -3018,7 +3018,7 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>1534766.92</v>
+        <v>209484</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -3026,16 +3026,16 @@
         <v>63</v>
       </c>
       <c r="B75">
-        <v>1679</v>
+        <v>25486</v>
       </c>
       <c r="C75">
-        <v>215.02</v>
+        <v>60.22</v>
       </c>
       <c r="D75">
-        <v>4365.4</v>
+        <v>-1274.3</v>
       </c>
       <c r="E75">
-        <v>361018.58</v>
+        <v>1534766.92</v>
       </c>
       <c r="F75" t="s">
         <v>161</v>
@@ -3047,7 +3047,7 @@
         <v>1</v>
       </c>
       <c r="I75">
-        <v>361018.58</v>
+        <v>1534766.92</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -3055,16 +3055,16 @@
         <v>64</v>
       </c>
       <c r="B76">
-        <v>8415</v>
+        <v>1679</v>
       </c>
       <c r="C76">
-        <v>96.289</v>
+        <v>215.02</v>
       </c>
       <c r="D76">
-        <v>17999.69</v>
+        <v>4365.4</v>
       </c>
       <c r="E76">
-        <v>810271.9399999999</v>
+        <v>361018.58</v>
       </c>
       <c r="F76" t="s">
         <v>161</v>
@@ -3076,7 +3076,7 @@
         <v>1</v>
       </c>
       <c r="I76">
-        <v>810271.9399999999</v>
+        <v>361018.58</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -3084,16 +3084,16 @@
         <v>65</v>
       </c>
       <c r="B77">
-        <v>75</v>
+        <v>8415</v>
       </c>
       <c r="C77">
-        <v>180.48</v>
+        <v>96.289</v>
       </c>
       <c r="D77">
-        <v>374.25</v>
+        <v>17999.69</v>
       </c>
       <c r="E77">
-        <v>13536</v>
+        <v>810271.9399999999</v>
       </c>
       <c r="F77" t="s">
         <v>161</v>
@@ -3105,7 +3105,7 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <v>13536</v>
+        <v>810271.9399999999</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3113,16 +3113,16 @@
         <v>66</v>
       </c>
       <c r="B78">
-        <v>11911</v>
+        <v>75</v>
       </c>
       <c r="C78">
-        <v>157.7</v>
+        <v>180.48</v>
       </c>
       <c r="D78">
-        <v>10005.24</v>
+        <v>374.25</v>
       </c>
       <c r="E78">
-        <v>1878364.7</v>
+        <v>13536</v>
       </c>
       <c r="F78" t="s">
         <v>161</v>
@@ -3134,7 +3134,7 @@
         <v>1</v>
       </c>
       <c r="I78">
-        <v>1878364.7</v>
+        <v>13536</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -3142,16 +3142,16 @@
         <v>67</v>
       </c>
       <c r="B79">
-        <v>75</v>
+        <v>11911</v>
       </c>
       <c r="C79">
-        <v>17.91</v>
+        <v>157.7</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>10005.24</v>
       </c>
       <c r="E79">
-        <v>1343.25</v>
+        <v>1878364.7</v>
       </c>
       <c r="F79" t="s">
         <v>161</v>
@@ -3163,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <v>1343.25</v>
+        <v>1878364.7</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -3171,16 +3171,16 @@
         <v>68</v>
       </c>
       <c r="B80">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="C80">
-        <v>610.58</v>
+        <v>17.91</v>
       </c>
       <c r="D80">
-        <v>76.34999999999999</v>
+        <v>0</v>
       </c>
       <c r="E80">
-        <v>9158.700000000001</v>
+        <v>1343.25</v>
       </c>
       <c r="F80" t="s">
         <v>161</v>
@@ -3192,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>9158.700000000001</v>
+        <v>1343.25</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -3200,16 +3200,16 @@
         <v>69</v>
       </c>
       <c r="B81">
-        <v>6067</v>
+        <v>15</v>
       </c>
       <c r="C81">
-        <v>179.44</v>
+        <v>610.58</v>
       </c>
       <c r="D81">
-        <v>8857.82</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="E81">
-        <v>1088662.48</v>
+        <v>9158.700000000001</v>
       </c>
       <c r="F81" t="s">
         <v>161</v>
@@ -3221,7 +3221,7 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <v>1088662.48</v>
+        <v>9158.700000000001</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3229,28 +3229,28 @@
         <v>70</v>
       </c>
       <c r="B82">
-        <v>179600</v>
+        <v>6067</v>
       </c>
       <c r="C82">
-        <v>17.37</v>
+        <v>179.44</v>
       </c>
       <c r="D82">
-        <v>13832.61</v>
+        <v>8857.82</v>
       </c>
       <c r="E82">
-        <v>3119652</v>
+        <v>1088662.48</v>
       </c>
       <c r="F82" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G82" t="s">
         <v>162</v>
       </c>
       <c r="H82">
-        <v>0.7702</v>
+        <v>1</v>
       </c>
       <c r="I82">
-        <v>2402755.97</v>
+        <v>1088662.48</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -3258,28 +3258,28 @@
         <v>71</v>
       </c>
       <c r="B83">
-        <v>75</v>
+        <v>179600</v>
       </c>
       <c r="C83">
-        <v>167.03</v>
+        <v>17.37</v>
       </c>
       <c r="D83">
-        <v>376.5</v>
+        <v>13832.61</v>
       </c>
       <c r="E83">
-        <v>12527.25</v>
+        <v>3119652</v>
       </c>
       <c r="F83" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G83" t="s">
         <v>162</v>
       </c>
       <c r="H83">
-        <v>1</v>
+        <v>0.7702</v>
       </c>
       <c r="I83">
-        <v>12527.25</v>
+        <v>2402755.97</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -3287,16 +3287,16 @@
         <v>72</v>
       </c>
       <c r="B84">
-        <v>10000</v>
+        <v>75</v>
       </c>
       <c r="C84">
-        <v>4.11</v>
+        <v>167.03</v>
       </c>
       <c r="D84">
-        <v>-1200</v>
+        <v>376.5</v>
       </c>
       <c r="E84">
-        <v>41100</v>
+        <v>12527.25</v>
       </c>
       <c r="F84" t="s">
         <v>161</v>
@@ -3308,7 +3308,7 @@
         <v>1</v>
       </c>
       <c r="I84">
-        <v>41100</v>
+        <v>12527.25</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -3316,16 +3316,16 @@
         <v>73</v>
       </c>
       <c r="B85">
-        <v>197</v>
+        <v>10000</v>
       </c>
       <c r="C85">
-        <v>72.54000000000001</v>
+        <v>4.11</v>
       </c>
       <c r="D85">
-        <v>-84.70999999999999</v>
+        <v>-1200</v>
       </c>
       <c r="E85">
-        <v>14290.38</v>
+        <v>41100</v>
       </c>
       <c r="F85" t="s">
         <v>161</v>
@@ -3337,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>14290.38</v>
+        <v>41100</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -3345,16 +3345,16 @@
         <v>74</v>
       </c>
       <c r="B86">
-        <v>97086</v>
+        <v>197</v>
       </c>
       <c r="C86">
-        <v>120.34</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="D86">
-        <v>84464.82000000001</v>
+        <v>-84.70999999999999</v>
       </c>
       <c r="E86">
-        <v>11683329.24</v>
+        <v>14290.38</v>
       </c>
       <c r="F86" t="s">
         <v>161</v>
@@ -3366,7 +3366,7 @@
         <v>1</v>
       </c>
       <c r="I86">
-        <v>11683329.24</v>
+        <v>14290.38</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -3374,16 +3374,16 @@
         <v>75</v>
       </c>
       <c r="B87">
-        <v>75</v>
+        <v>97086</v>
       </c>
       <c r="C87">
-        <v>214.84</v>
+        <v>120.34</v>
       </c>
       <c r="D87">
-        <v>265.5</v>
+        <v>84464.82000000001</v>
       </c>
       <c r="E87">
-        <v>16113</v>
+        <v>11683329.24</v>
       </c>
       <c r="F87" t="s">
         <v>161</v>
@@ -3395,7 +3395,7 @@
         <v>1</v>
       </c>
       <c r="I87">
-        <v>16113</v>
+        <v>11683329.24</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -3403,16 +3403,16 @@
         <v>76</v>
       </c>
       <c r="B88">
-        <v>181</v>
+        <v>75</v>
       </c>
       <c r="C88">
-        <v>139.72</v>
+        <v>214.84</v>
       </c>
       <c r="D88">
-        <v>-86.88</v>
+        <v>265.5</v>
       </c>
       <c r="E88">
-        <v>25289.32</v>
+        <v>16113</v>
       </c>
       <c r="F88" t="s">
         <v>161</v>
@@ -3424,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="I88">
-        <v>25289.32</v>
+        <v>16113</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -3432,16 +3432,16 @@
         <v>77</v>
       </c>
       <c r="B89">
-        <v>146672</v>
+        <v>181</v>
       </c>
       <c r="C89">
-        <v>107.22</v>
+        <v>139.72</v>
       </c>
       <c r="D89">
-        <v>516337.03</v>
+        <v>-86.88</v>
       </c>
       <c r="E89">
-        <v>15726171.84</v>
+        <v>25289.32</v>
       </c>
       <c r="F89" t="s">
         <v>161</v>
@@ -3453,7 +3453,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <v>15726171.84</v>
+        <v>25289.32</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -3461,16 +3461,16 @@
         <v>78</v>
       </c>
       <c r="B90">
-        <v>120</v>
+        <v>146672</v>
       </c>
       <c r="C90">
-        <v>290.73</v>
+        <v>107.22</v>
       </c>
       <c r="D90">
-        <v>222</v>
+        <v>516337.03</v>
       </c>
       <c r="E90">
-        <v>34887.6</v>
+        <v>15726171.84</v>
       </c>
       <c r="F90" t="s">
         <v>161</v>
@@ -3482,7 +3482,7 @@
         <v>1</v>
       </c>
       <c r="I90">
-        <v>34887.6</v>
+        <v>15726171.84</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -3490,28 +3490,28 @@
         <v>79</v>
       </c>
       <c r="B91">
-        <v>1621700</v>
+        <v>120</v>
       </c>
       <c r="C91">
-        <v>6.45</v>
+        <v>290.73</v>
       </c>
       <c r="D91">
-        <v>12490.17</v>
+        <v>222</v>
       </c>
       <c r="E91">
-        <v>10459965</v>
+        <v>34887.6</v>
       </c>
       <c r="F91" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G91" t="s">
         <v>162</v>
       </c>
       <c r="H91">
-        <v>0.7702</v>
+        <v>1</v>
       </c>
       <c r="I91">
-        <v>8056265.04</v>
+        <v>34887.6</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -3519,28 +3519,28 @@
         <v>80</v>
       </c>
       <c r="B92">
-        <v>15</v>
+        <v>1621700</v>
       </c>
       <c r="C92">
-        <v>94.43000000000001</v>
+        <v>6.45</v>
       </c>
       <c r="D92">
-        <v>-3.75</v>
+        <v>12490.17</v>
       </c>
       <c r="E92">
-        <v>1416.45</v>
+        <v>10459965</v>
       </c>
       <c r="F92" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G92" t="s">
         <v>162</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>0.7702</v>
       </c>
       <c r="I92">
-        <v>1416.45</v>
+        <v>8056265.04</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -3548,16 +3548,16 @@
         <v>81</v>
       </c>
       <c r="B93">
-        <v>187757</v>
+        <v>15</v>
       </c>
       <c r="C93">
-        <v>10.44</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="D93">
-        <v>-47729.64</v>
+        <v>-3.75</v>
       </c>
       <c r="E93">
-        <v>1960183.08</v>
+        <v>1416.45</v>
       </c>
       <c r="F93" t="s">
         <v>161</v>
@@ -3569,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>1960183.08</v>
+        <v>1416.45</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -3577,16 +3577,16 @@
         <v>82</v>
       </c>
       <c r="B94">
-        <v>61072</v>
+        <v>187757</v>
       </c>
       <c r="C94">
-        <v>32.6</v>
+        <v>10.44</v>
       </c>
       <c r="D94">
-        <v>-29076.07</v>
+        <v>-47729.64</v>
       </c>
       <c r="E94">
-        <v>1990947.2</v>
+        <v>1960183.08</v>
       </c>
       <c r="F94" t="s">
         <v>161</v>
@@ -3598,7 +3598,7 @@
         <v>1</v>
       </c>
       <c r="I94">
-        <v>1990947.2</v>
+        <v>1960183.08</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -3606,16 +3606,16 @@
         <v>83</v>
       </c>
       <c r="B95">
-        <v>1054</v>
+        <v>61072</v>
       </c>
       <c r="C95">
-        <v>183.2</v>
+        <v>32.6</v>
       </c>
       <c r="D95">
-        <v>12236.94</v>
+        <v>-29076.07</v>
       </c>
       <c r="E95">
-        <v>193092.8</v>
+        <v>1990947.2</v>
       </c>
       <c r="F95" t="s">
         <v>161</v>
@@ -3627,7 +3627,7 @@
         <v>1</v>
       </c>
       <c r="I95">
-        <v>193092.8</v>
+        <v>1990947.2</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -3635,16 +3635,16 @@
         <v>84</v>
       </c>
       <c r="B96">
-        <v>5000</v>
+        <v>1054</v>
       </c>
       <c r="C96">
-        <v>191.37</v>
+        <v>183.2</v>
       </c>
       <c r="D96">
-        <v>27700</v>
+        <v>12236.94</v>
       </c>
       <c r="E96">
-        <v>956850</v>
+        <v>193092.8</v>
       </c>
       <c r="F96" t="s">
         <v>161</v>
@@ -3656,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="I96">
-        <v>956850</v>
+        <v>193092.8</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -3664,16 +3664,16 @@
         <v>85</v>
       </c>
       <c r="B97">
-        <v>58601</v>
+        <v>5000</v>
       </c>
       <c r="C97">
-        <v>33.47</v>
+        <v>191.37</v>
       </c>
       <c r="D97">
-        <v>-35338.59</v>
+        <v>27700</v>
       </c>
       <c r="E97">
-        <v>1961375.47</v>
+        <v>956850</v>
       </c>
       <c r="F97" t="s">
         <v>161</v>
@@ -3685,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>1961375.47</v>
+        <v>956850</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3693,16 +3693,16 @@
         <v>86</v>
       </c>
       <c r="B98">
-        <v>17214</v>
+        <v>58601</v>
       </c>
       <c r="C98">
-        <v>38.4</v>
+        <v>33.47</v>
       </c>
       <c r="D98">
-        <v>-24099.6</v>
+        <v>-35338.59</v>
       </c>
       <c r="E98">
-        <v>661017.6</v>
+        <v>1961375.47</v>
       </c>
       <c r="F98" t="s">
         <v>161</v>
@@ -3714,7 +3714,7 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>661017.6</v>
+        <v>1961375.47</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -3722,16 +3722,16 @@
         <v>87</v>
       </c>
       <c r="B99">
-        <v>46680</v>
+        <v>17214</v>
       </c>
       <c r="C99">
-        <v>73.34</v>
+        <v>38.4</v>
       </c>
       <c r="D99">
-        <v>33142.8</v>
+        <v>-24099.6</v>
       </c>
       <c r="E99">
-        <v>3423511.2</v>
+        <v>661017.6</v>
       </c>
       <c r="F99" t="s">
         <v>161</v>
@@ -3743,7 +3743,7 @@
         <v>1</v>
       </c>
       <c r="I99">
-        <v>3423511.2</v>
+        <v>661017.6</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -3751,28 +3751,28 @@
         <v>88</v>
       </c>
       <c r="B100">
-        <v>81000</v>
+        <v>46680</v>
       </c>
       <c r="C100">
-        <v>74.92</v>
+        <v>73.34</v>
       </c>
       <c r="D100">
-        <v>-12150</v>
+        <v>33142.8</v>
       </c>
       <c r="E100">
-        <v>6068520</v>
+        <v>3423511.2</v>
       </c>
       <c r="F100" t="s">
         <v>161</v>
       </c>
       <c r="G100" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H100">
         <v>1</v>
       </c>
       <c r="I100">
-        <v>6068520</v>
+        <v>3423511.2</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -3780,16 +3780,16 @@
         <v>89</v>
       </c>
       <c r="B101">
-        <v>316025</v>
+        <v>81000</v>
       </c>
       <c r="C101">
-        <v>21.32</v>
+        <v>74.92</v>
       </c>
       <c r="D101">
-        <v>-3160.25</v>
+        <v>-12150</v>
       </c>
       <c r="E101">
-        <v>6737653</v>
+        <v>6068520</v>
       </c>
       <c r="F101" t="s">
         <v>161</v>
@@ -3801,7 +3801,7 @@
         <v>1</v>
       </c>
       <c r="I101">
-        <v>6737653</v>
+        <v>6068520</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -3809,16 +3809,16 @@
         <v>90</v>
       </c>
       <c r="B102">
-        <v>193065</v>
+        <v>316025</v>
       </c>
       <c r="C102">
-        <v>25.5</v>
+        <v>21.32</v>
       </c>
       <c r="D102">
-        <v>5791.95</v>
+        <v>-3160.25</v>
       </c>
       <c r="E102">
-        <v>4923157.5</v>
+        <v>6737653</v>
       </c>
       <c r="F102" t="s">
         <v>161</v>
@@ -3830,7 +3830,7 @@
         <v>1</v>
       </c>
       <c r="I102">
-        <v>4923157.5</v>
+        <v>6737653</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3838,16 +3838,16 @@
         <v>91</v>
       </c>
       <c r="B103">
-        <v>112925</v>
+        <v>193065</v>
       </c>
       <c r="C103">
-        <v>100.62</v>
+        <v>25.5</v>
       </c>
       <c r="D103">
-        <v>1129.25</v>
+        <v>5791.95</v>
       </c>
       <c r="E103">
-        <v>11362513.5</v>
+        <v>4923157.5</v>
       </c>
       <c r="F103" t="s">
         <v>161</v>
@@ -3859,7 +3859,7 @@
         <v>1</v>
       </c>
       <c r="I103">
-        <v>11362513.5</v>
+        <v>4923157.5</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3867,16 +3867,16 @@
         <v>92</v>
       </c>
       <c r="B104">
-        <v>82878</v>
+        <v>112925</v>
       </c>
       <c r="C104">
-        <v>43.07</v>
+        <v>100.62</v>
       </c>
       <c r="D104">
-        <v>4143.9</v>
+        <v>1129.25</v>
       </c>
       <c r="E104">
-        <v>3569555.46</v>
+        <v>11362513.5</v>
       </c>
       <c r="F104" t="s">
         <v>161</v>
@@ -3888,7 +3888,7 @@
         <v>1</v>
       </c>
       <c r="I104">
-        <v>3569555.46</v>
+        <v>11362513.5</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3896,28 +3896,28 @@
         <v>93</v>
       </c>
       <c r="B105">
-        <v>29600</v>
+        <v>82878</v>
       </c>
       <c r="C105">
-        <v>80.43000000000001</v>
+        <v>43.07</v>
       </c>
       <c r="D105">
-        <v>27232</v>
+        <v>4143.9</v>
       </c>
       <c r="E105">
-        <v>2380728</v>
+        <v>3569555.46</v>
       </c>
       <c r="F105" t="s">
         <v>161</v>
       </c>
       <c r="G105" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H105">
         <v>1</v>
       </c>
       <c r="I105">
-        <v>2380728</v>
+        <v>3569555.46</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -3925,16 +3925,16 @@
         <v>94</v>
       </c>
       <c r="B106">
-        <v>16400</v>
+        <v>29600</v>
       </c>
       <c r="C106">
-        <v>73.79000000000001</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="D106">
-        <v>13776</v>
+        <v>27232</v>
       </c>
       <c r="E106">
-        <v>1210156</v>
+        <v>2380728</v>
       </c>
       <c r="F106" t="s">
         <v>161</v>
@@ -3946,7 +3946,7 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>1210156</v>
+        <v>2380728</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -3954,16 +3954,16 @@
         <v>95</v>
       </c>
       <c r="B107">
-        <v>44035</v>
+        <v>16400</v>
       </c>
       <c r="C107">
-        <v>41.03</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="D107">
-        <v>5724.55</v>
+        <v>13776</v>
       </c>
       <c r="E107">
-        <v>1806756.05</v>
+        <v>1210156</v>
       </c>
       <c r="F107" t="s">
         <v>161</v>
@@ -3975,7 +3975,7 @@
         <v>1</v>
       </c>
       <c r="I107">
-        <v>1806756.05</v>
+        <v>1210156</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -3983,16 +3983,16 @@
         <v>96</v>
       </c>
       <c r="B108">
-        <v>27331</v>
+        <v>44035</v>
       </c>
       <c r="C108">
-        <v>62.56</v>
+        <v>41.03</v>
       </c>
       <c r="D108">
-        <v>36896.85</v>
+        <v>5724.55</v>
       </c>
       <c r="E108">
-        <v>1709827.36</v>
+        <v>1806756.05</v>
       </c>
       <c r="F108" t="s">
         <v>161</v>
@@ -4004,7 +4004,7 @@
         <v>1</v>
       </c>
       <c r="I108">
-        <v>1709827.36</v>
+        <v>1806756.05</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -4012,16 +4012,16 @@
         <v>97</v>
       </c>
       <c r="B109">
-        <v>26700</v>
+        <v>27331</v>
       </c>
       <c r="C109">
-        <v>49.94</v>
+        <v>62.56</v>
       </c>
       <c r="D109">
-        <v>26700</v>
+        <v>36896.85</v>
       </c>
       <c r="E109">
-        <v>1333398</v>
+        <v>1709827.36</v>
       </c>
       <c r="F109" t="s">
         <v>161</v>
@@ -4033,7 +4033,7 @@
         <v>1</v>
       </c>
       <c r="I109">
-        <v>1333398</v>
+        <v>1709827.36</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -4041,16 +4041,16 @@
         <v>98</v>
       </c>
       <c r="B110">
-        <v>14556</v>
+        <v>26700</v>
       </c>
       <c r="C110">
-        <v>83.75</v>
+        <v>49.94</v>
       </c>
       <c r="D110">
-        <v>7423.56</v>
+        <v>26700</v>
       </c>
       <c r="E110">
-        <v>1219065</v>
+        <v>1333398</v>
       </c>
       <c r="F110" t="s">
         <v>161</v>
@@ -4062,7 +4062,7 @@
         <v>1</v>
       </c>
       <c r="I110">
-        <v>1219065</v>
+        <v>1333398</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -4070,28 +4070,28 @@
         <v>99</v>
       </c>
       <c r="B111">
-        <v>56708</v>
+        <v>14556</v>
       </c>
       <c r="C111">
-        <v>107.205</v>
+        <v>83.75</v>
       </c>
       <c r="D111">
-        <v>5103.72</v>
+        <v>7423.56</v>
       </c>
       <c r="E111">
-        <v>6079381.14</v>
+        <v>1219065</v>
       </c>
       <c r="F111" t="s">
         <v>161</v>
       </c>
       <c r="G111" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H111">
         <v>1</v>
       </c>
       <c r="I111">
-        <v>6079381.14</v>
+        <v>1219065</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -4099,16 +4099,16 @@
         <v>100</v>
       </c>
       <c r="B112">
-        <v>53604</v>
+        <v>56708</v>
       </c>
       <c r="C112">
-        <v>111.28</v>
+        <v>107.205</v>
       </c>
       <c r="D112">
-        <v>6453.92</v>
+        <v>5103.72</v>
       </c>
       <c r="E112">
-        <v>5965053.12</v>
+        <v>6079381.14</v>
       </c>
       <c r="F112" t="s">
         <v>161</v>
@@ -4120,7 +4120,7 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>5965053.12</v>
+        <v>6079381.14</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -4128,16 +4128,16 @@
         <v>101</v>
       </c>
       <c r="B113">
-        <v>96750</v>
+        <v>53604</v>
       </c>
       <c r="C113">
-        <v>60.3</v>
+        <v>111.28</v>
       </c>
       <c r="D113">
-        <v>-20317.5</v>
+        <v>6453.92</v>
       </c>
       <c r="E113">
-        <v>5834025</v>
+        <v>5965053.12</v>
       </c>
       <c r="F113" t="s">
         <v>161</v>
@@ -4149,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>5834025</v>
+        <v>5965053.12</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -4157,28 +4157,28 @@
         <v>102</v>
       </c>
       <c r="B114">
-        <v>-50</v>
+        <v>96750</v>
       </c>
       <c r="C114">
-        <v>41.31</v>
+        <v>60.3</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>-20317.5</v>
       </c>
       <c r="E114">
-        <v>-2065.5</v>
+        <v>5834025</v>
       </c>
       <c r="F114" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G114" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H114">
-        <v>0.1287</v>
+        <v>1</v>
       </c>
       <c r="I114">
-        <v>-265.83</v>
+        <v>5834025</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -4186,16 +4186,16 @@
         <v>103</v>
       </c>
       <c r="B115">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="C115">
-        <v>33.88</v>
+        <v>41.31</v>
       </c>
       <c r="D115">
-        <v>-617.62</v>
+        <v>0</v>
       </c>
       <c r="E115">
-        <v>1694</v>
+        <v>-2065.5</v>
       </c>
       <c r="F115" t="s">
         <v>158</v>
@@ -4207,7 +4207,7 @@
         <v>0.1287</v>
       </c>
       <c r="I115">
-        <v>218.02</v>
+        <v>-265.83</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -4215,16 +4215,16 @@
         <v>104</v>
       </c>
       <c r="B116">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="C116">
-        <v>54.77</v>
+        <v>33.88</v>
       </c>
       <c r="D116">
-        <v>-591.88</v>
+        <v>-617.62</v>
       </c>
       <c r="E116">
-        <v>-5477</v>
+        <v>1694</v>
       </c>
       <c r="F116" t="s">
         <v>158</v>
@@ -4236,7 +4236,7 @@
         <v>0.1287</v>
       </c>
       <c r="I116">
-        <v>-704.89</v>
+        <v>218.02</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -4244,16 +4244,16 @@
         <v>105</v>
       </c>
       <c r="B117">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="C117">
-        <v>34.51</v>
+        <v>54.77</v>
       </c>
       <c r="D117">
-        <v>-1248.1</v>
+        <v>-591.88</v>
       </c>
       <c r="E117">
-        <v>3451</v>
+        <v>-5477</v>
       </c>
       <c r="F117" t="s">
         <v>158</v>
@@ -4265,7 +4265,7 @@
         <v>0.1287</v>
       </c>
       <c r="I117">
-        <v>444.14</v>
+        <v>-704.89</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -4273,28 +4273,28 @@
         <v>106</v>
       </c>
       <c r="B118">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="C118">
-        <v>4.4255</v>
+        <v>34.51</v>
       </c>
       <c r="D118">
-        <v>7644</v>
+        <v>-1248.1</v>
       </c>
       <c r="E118">
-        <v>1327.65</v>
+        <v>3451</v>
       </c>
       <c r="F118" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G118" t="s">
         <v>166</v>
       </c>
       <c r="H118">
-        <v>1</v>
+        <v>0.1287</v>
       </c>
       <c r="I118">
-        <v>1327.65</v>
+        <v>444.14</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -4302,16 +4302,16 @@
         <v>107</v>
       </c>
       <c r="B119">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="C119">
-        <v>5.4342</v>
+        <v>4.4255</v>
       </c>
       <c r="D119">
-        <v>720</v>
+        <v>7644</v>
       </c>
       <c r="E119">
-        <v>-1086.84</v>
+        <v>1327.65</v>
       </c>
       <c r="F119" t="s">
         <v>161</v>
@@ -4323,7 +4323,7 @@
         <v>1</v>
       </c>
       <c r="I119">
-        <v>-1086.84</v>
+        <v>1327.65</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -4331,16 +4331,16 @@
         <v>108</v>
       </c>
       <c r="B120">
-        <v>-10</v>
+        <v>-200</v>
       </c>
       <c r="C120">
-        <v>51.3196</v>
+        <v>5.4342</v>
       </c>
       <c r="D120">
-        <v>685.5</v>
+        <v>720</v>
       </c>
       <c r="E120">
-        <v>-513.2</v>
+        <v>-1086.84</v>
       </c>
       <c r="F120" t="s">
         <v>161</v>
@@ -4352,7 +4352,7 @@
         <v>1</v>
       </c>
       <c r="I120">
-        <v>-513.2</v>
+        <v>-1086.84</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -4360,16 +4360,16 @@
         <v>109</v>
       </c>
       <c r="B121">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="C121">
-        <v>57.3305</v>
+        <v>51.3196</v>
       </c>
       <c r="D121">
-        <v>715.35</v>
+        <v>685.5</v>
       </c>
       <c r="E121">
-        <v>-859.96</v>
+        <v>-513.2</v>
       </c>
       <c r="F121" t="s">
         <v>161</v>
@@ -4381,7 +4381,7 @@
         <v>1</v>
       </c>
       <c r="I121">
-        <v>-859.96</v>
+        <v>-513.2</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -4389,16 +4389,16 @@
         <v>110</v>
       </c>
       <c r="B122">
-        <v>20</v>
+        <v>-15</v>
       </c>
       <c r="C122">
-        <v>31.175</v>
+        <v>57.3305</v>
       </c>
       <c r="D122">
-        <v>1302.2</v>
+        <v>715.35</v>
       </c>
       <c r="E122">
-        <v>623.5</v>
+        <v>-859.96</v>
       </c>
       <c r="F122" t="s">
         <v>161</v>
@@ -4410,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="I122">
-        <v>623.5</v>
+        <v>-859.96</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -4418,16 +4418,16 @@
         <v>111</v>
       </c>
       <c r="B123">
-        <v>-8</v>
+        <v>20</v>
       </c>
       <c r="C123">
-        <v>95.0976</v>
+        <v>31.175</v>
       </c>
       <c r="D123">
-        <v>2502.56</v>
+        <v>1302.2</v>
       </c>
       <c r="E123">
-        <v>-760.78</v>
+        <v>623.5</v>
       </c>
       <c r="F123" t="s">
         <v>161</v>
@@ -4439,7 +4439,7 @@
         <v>1</v>
       </c>
       <c r="I123">
-        <v>-760.78</v>
+        <v>623.5</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -4447,16 +4447,16 @@
         <v>112</v>
       </c>
       <c r="B124">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="C124">
-        <v>99.3685</v>
+        <v>95.0976</v>
       </c>
       <c r="D124">
-        <v>688.6</v>
+        <v>2502.56</v>
       </c>
       <c r="E124">
-        <v>-198.74</v>
+        <v>-760.78</v>
       </c>
       <c r="F124" t="s">
         <v>161</v>
@@ -4468,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="I124">
-        <v>-198.74</v>
+        <v>-760.78</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -4476,16 +4476,16 @@
         <v>113</v>
       </c>
       <c r="B125">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="C125">
-        <v>122.15</v>
+        <v>99.3685</v>
       </c>
       <c r="D125">
-        <v>4062.4</v>
+        <v>688.6</v>
       </c>
       <c r="E125">
-        <v>-1221.5</v>
+        <v>-198.74</v>
       </c>
       <c r="F125" t="s">
         <v>161</v>
@@ -4497,7 +4497,7 @@
         <v>1</v>
       </c>
       <c r="I125">
-        <v>-1221.5</v>
+        <v>-198.74</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -4505,16 +4505,16 @@
         <v>114</v>
       </c>
       <c r="B126">
-        <v>8</v>
+        <v>-10</v>
       </c>
       <c r="C126">
-        <v>112.8151</v>
+        <v>122.15</v>
       </c>
       <c r="D126">
-        <v>2190.56</v>
+        <v>4062.4</v>
       </c>
       <c r="E126">
-        <v>902.52</v>
+        <v>-1221.5</v>
       </c>
       <c r="F126" t="s">
         <v>161</v>
@@ -4526,7 +4526,7 @@
         <v>1</v>
       </c>
       <c r="I126">
-        <v>902.52</v>
+        <v>-1221.5</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -4534,16 +4534,16 @@
         <v>115</v>
       </c>
       <c r="B127">
-        <v>-8</v>
+        <v>8</v>
       </c>
       <c r="C127">
-        <v>153.6592</v>
+        <v>112.8151</v>
       </c>
       <c r="D127">
-        <v>3730.08</v>
+        <v>2190.56</v>
       </c>
       <c r="E127">
-        <v>-1229.27</v>
+        <v>902.52</v>
       </c>
       <c r="F127" t="s">
         <v>161</v>
@@ -4555,7 +4555,7 @@
         <v>1</v>
       </c>
       <c r="I127">
-        <v>-1229.27</v>
+        <v>902.52</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -4563,16 +4563,16 @@
         <v>116</v>
       </c>
       <c r="B128">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="C128">
-        <v>87.15860000000001</v>
+        <v>153.6592</v>
       </c>
       <c r="D128">
-        <v>698.6</v>
+        <v>3730.08</v>
       </c>
       <c r="E128">
-        <v>435.79</v>
+        <v>-1229.27</v>
       </c>
       <c r="F128" t="s">
         <v>161</v>
@@ -4584,7 +4584,7 @@
         <v>1</v>
       </c>
       <c r="I128">
-        <v>435.79</v>
+        <v>-1229.27</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -4592,16 +4592,16 @@
         <v>117</v>
       </c>
       <c r="B129">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="C129">
-        <v>32.4251</v>
+        <v>87.15860000000001</v>
       </c>
       <c r="D129">
-        <v>100</v>
+        <v>698.6</v>
       </c>
       <c r="E129">
-        <v>-324.25</v>
+        <v>435.79</v>
       </c>
       <c r="F129" t="s">
         <v>161</v>
@@ -4613,7 +4613,7 @@
         <v>1</v>
       </c>
       <c r="I129">
-        <v>-324.25</v>
+        <v>435.79</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -4621,16 +4621,16 @@
         <v>118</v>
       </c>
       <c r="B130">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="C130">
-        <v>46.1002</v>
+        <v>32.4251</v>
       </c>
       <c r="D130">
-        <v>2018.7</v>
+        <v>100</v>
       </c>
       <c r="E130">
-        <v>-1383.01</v>
+        <v>-324.25</v>
       </c>
       <c r="F130" t="s">
         <v>161</v>
@@ -4642,7 +4642,7 @@
         <v>1</v>
       </c>
       <c r="I130">
-        <v>-1383.01</v>
+        <v>-324.25</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -4650,16 +4650,16 @@
         <v>119</v>
       </c>
       <c r="B131">
-        <v>15</v>
+        <v>-30</v>
       </c>
       <c r="C131">
-        <v>36.4577</v>
+        <v>46.1002</v>
       </c>
       <c r="D131">
-        <v>476.1</v>
+        <v>2018.7</v>
       </c>
       <c r="E131">
-        <v>546.87</v>
+        <v>-1383.01</v>
       </c>
       <c r="F131" t="s">
         <v>161</v>
@@ -4671,7 +4671,7 @@
         <v>1</v>
       </c>
       <c r="I131">
-        <v>546.87</v>
+        <v>-1383.01</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -4679,16 +4679,16 @@
         <v>120</v>
       </c>
       <c r="B132">
-        <v>-15</v>
+        <v>15</v>
       </c>
       <c r="C132">
-        <v>51.3154</v>
+        <v>36.4577</v>
       </c>
       <c r="D132">
-        <v>1436.55</v>
+        <v>476.1</v>
       </c>
       <c r="E132">
-        <v>-769.73</v>
+        <v>546.87</v>
       </c>
       <c r="F132" t="s">
         <v>161</v>
@@ -4700,7 +4700,7 @@
         <v>1</v>
       </c>
       <c r="I132">
-        <v>-769.73</v>
+        <v>546.87</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -4708,16 +4708,16 @@
         <v>121</v>
       </c>
       <c r="B133">
-        <v>10</v>
+        <v>-15</v>
       </c>
       <c r="C133">
-        <v>32.8435</v>
+        <v>51.3154</v>
       </c>
       <c r="D133">
-        <v>768.9</v>
+        <v>1436.55</v>
       </c>
       <c r="E133">
-        <v>328.44</v>
+        <v>-769.73</v>
       </c>
       <c r="F133" t="s">
         <v>161</v>
@@ -4729,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="I133">
-        <v>328.44</v>
+        <v>-769.73</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -4737,16 +4737,16 @@
         <v>122</v>
       </c>
       <c r="B134">
-        <v>-30</v>
+        <v>10</v>
       </c>
       <c r="C134">
-        <v>57.3293</v>
+        <v>32.8435</v>
       </c>
       <c r="D134">
-        <v>1479.9</v>
+        <v>768.9</v>
       </c>
       <c r="E134">
-        <v>-1719.88</v>
+        <v>328.44</v>
       </c>
       <c r="F134" t="s">
         <v>161</v>
@@ -4758,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="I134">
-        <v>-1719.88</v>
+        <v>328.44</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -4766,16 +4766,16 @@
         <v>123</v>
       </c>
       <c r="B135">
-        <v>-15</v>
+        <v>-30</v>
       </c>
       <c r="C135">
-        <v>76.4949</v>
+        <v>57.3293</v>
       </c>
       <c r="D135">
-        <v>1491.9</v>
+        <v>1479.9</v>
       </c>
       <c r="E135">
-        <v>-1147.42</v>
+        <v>-1719.88</v>
       </c>
       <c r="F135" t="s">
         <v>161</v>
@@ -4787,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="I135">
-        <v>-1147.42</v>
+        <v>-1719.88</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -4795,16 +4795,16 @@
         <v>124</v>
       </c>
       <c r="B136">
-        <v>20</v>
+        <v>-15</v>
       </c>
       <c r="C136">
-        <v>5.5751</v>
+        <v>76.4949</v>
       </c>
       <c r="D136">
-        <v>100</v>
+        <v>1491.9</v>
       </c>
       <c r="E136">
-        <v>111.5</v>
+        <v>-1147.42</v>
       </c>
       <c r="F136" t="s">
         <v>161</v>
@@ -4816,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="I136">
-        <v>111.5</v>
+        <v>-1147.42</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -4824,16 +4824,16 @@
         <v>125</v>
       </c>
       <c r="B137">
-        <v>-50</v>
+        <v>20</v>
       </c>
       <c r="C137">
-        <v>1237.5</v>
+        <v>5.5751</v>
       </c>
       <c r="D137">
-        <v>-118250</v>
+        <v>100</v>
       </c>
       <c r="E137">
-        <v>-61875</v>
+        <v>111.5</v>
       </c>
       <c r="F137" t="s">
         <v>161</v>
@@ -4845,7 +4845,7 @@
         <v>1</v>
       </c>
       <c r="I137">
-        <v>-61875</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -4853,16 +4853,16 @@
         <v>126</v>
       </c>
       <c r="B138">
-        <v>25</v>
+        <v>-50</v>
       </c>
       <c r="C138">
-        <v>481.75</v>
+        <v>1237.5</v>
       </c>
       <c r="D138">
-        <v>32625</v>
+        <v>-118250</v>
       </c>
       <c r="E138">
-        <v>12043.75</v>
+        <v>-61875</v>
       </c>
       <c r="F138" t="s">
         <v>161</v>
@@ -4874,7 +4874,7 @@
         <v>1</v>
       </c>
       <c r="I138">
-        <v>12043.75</v>
+        <v>-61875</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -4885,13 +4885,13 @@
         <v>25</v>
       </c>
       <c r="C139">
-        <v>377.75</v>
+        <v>481.75</v>
       </c>
       <c r="D139">
-        <v>27375</v>
+        <v>32625</v>
       </c>
       <c r="E139">
-        <v>9443.75</v>
+        <v>12043.75</v>
       </c>
       <c r="F139" t="s">
         <v>161</v>
@@ -4903,7 +4903,7 @@
         <v>1</v>
       </c>
       <c r="I139">
-        <v>9443.75</v>
+        <v>12043.75</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -4911,16 +4911,16 @@
         <v>128</v>
       </c>
       <c r="B140">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C140">
-        <v>128.3954</v>
+        <v>377.75</v>
       </c>
       <c r="D140">
-        <v>6304.9</v>
+        <v>27375</v>
       </c>
       <c r="E140">
-        <v>1283.95</v>
+        <v>9443.75</v>
       </c>
       <c r="F140" t="s">
         <v>161</v>
@@ -4932,7 +4932,7 @@
         <v>1</v>
       </c>
       <c r="I140">
-        <v>1283.95</v>
+        <v>9443.75</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -4940,16 +4940,16 @@
         <v>129</v>
       </c>
       <c r="B141">
-        <v>-20</v>
+        <v>10</v>
       </c>
       <c r="C141">
-        <v>91.9966</v>
+        <v>128.3954</v>
       </c>
       <c r="D141">
-        <v>6669.8</v>
+        <v>6304.9</v>
       </c>
       <c r="E141">
-        <v>-1839.93</v>
+        <v>1283.95</v>
       </c>
       <c r="F141" t="s">
         <v>161</v>
@@ -4961,7 +4961,7 @@
         <v>1</v>
       </c>
       <c r="I141">
-        <v>-1839.93</v>
+        <v>1283.95</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -4969,16 +4969,16 @@
         <v>130</v>
       </c>
       <c r="B142">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="C142">
-        <v>31.175</v>
+        <v>91.9966</v>
       </c>
       <c r="D142">
-        <v>5100.8</v>
+        <v>6669.8</v>
       </c>
       <c r="E142">
-        <v>-1247</v>
+        <v>-1839.93</v>
       </c>
       <c r="F142" t="s">
         <v>161</v>
@@ -4990,7 +4990,7 @@
         <v>1</v>
       </c>
       <c r="I142">
-        <v>-1247</v>
+        <v>-1839.93</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -4998,16 +4998,16 @@
         <v>131</v>
       </c>
       <c r="B143">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="C143">
-        <v>52.175</v>
+        <v>31.175</v>
       </c>
       <c r="D143">
-        <v>11313</v>
+        <v>5100.8</v>
       </c>
       <c r="E143">
-        <v>-3130.5</v>
+        <v>-1247</v>
       </c>
       <c r="F143" t="s">
         <v>161</v>
@@ -5019,7 +5019,7 @@
         <v>1</v>
       </c>
       <c r="I143">
-        <v>-3130.5</v>
+        <v>-1247</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -5027,16 +5027,16 @@
         <v>132</v>
       </c>
       <c r="B144">
-        <v>-10</v>
+        <v>-60</v>
       </c>
       <c r="C144">
-        <v>55.125</v>
+        <v>52.175</v>
       </c>
       <c r="D144">
-        <v>1883.5</v>
+        <v>11313</v>
       </c>
       <c r="E144">
-        <v>-551.25</v>
+        <v>-3130.5</v>
       </c>
       <c r="F144" t="s">
         <v>161</v>
@@ -5048,7 +5048,7 @@
         <v>1</v>
       </c>
       <c r="I144">
-        <v>-551.25</v>
+        <v>-3130.5</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -5059,13 +5059,13 @@
         <v>-10</v>
       </c>
       <c r="C145">
-        <v>61.1499</v>
+        <v>55.125</v>
       </c>
       <c r="D145">
-        <v>2145</v>
+        <v>1883.5</v>
       </c>
       <c r="E145">
-        <v>-611.5</v>
+        <v>-551.25</v>
       </c>
       <c r="F145" t="s">
         <v>161</v>
@@ -5077,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="I145">
-        <v>-611.5</v>
+        <v>-551.25</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -5085,16 +5085,16 @@
         <v>134</v>
       </c>
       <c r="B146">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="C146">
-        <v>42.175</v>
+        <v>61.1499</v>
       </c>
       <c r="D146">
-        <v>2525</v>
+        <v>2145</v>
       </c>
       <c r="E146">
-        <v>421.75</v>
+        <v>-611.5</v>
       </c>
       <c r="F146" t="s">
         <v>161</v>
@@ -5106,7 +5106,7 @@
         <v>1</v>
       </c>
       <c r="I146">
-        <v>421.75</v>
+        <v>-611.5</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -5114,16 +5114,16 @@
         <v>135</v>
       </c>
       <c r="B147">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C147">
-        <v>38.125</v>
+        <v>42.175</v>
       </c>
       <c r="D147">
-        <v>7275</v>
+        <v>2525</v>
       </c>
       <c r="E147">
-        <v>1143.75</v>
+        <v>421.75</v>
       </c>
       <c r="F147" t="s">
         <v>161</v>
@@ -5135,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="I147">
-        <v>1143.75</v>
+        <v>421.75</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -5143,16 +5143,16 @@
         <v>136</v>
       </c>
       <c r="B148">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C148">
-        <v>46.8419</v>
+        <v>38.125</v>
       </c>
       <c r="D148">
-        <v>1226.64</v>
+        <v>7275</v>
       </c>
       <c r="E148">
-        <v>1124.21</v>
+        <v>1143.75</v>
       </c>
       <c r="F148" t="s">
         <v>161</v>
@@ -5164,7 +5164,7 @@
         <v>1</v>
       </c>
       <c r="I148">
-        <v>1124.21</v>
+        <v>1143.75</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -5172,16 +5172,16 @@
         <v>137</v>
       </c>
       <c r="B149">
-        <v>-48</v>
+        <v>24</v>
       </c>
       <c r="C149">
-        <v>38.0316</v>
+        <v>46.8419</v>
       </c>
       <c r="D149">
-        <v>3230.88</v>
+        <v>1226.64</v>
       </c>
       <c r="E149">
-        <v>-1825.52</v>
+        <v>1124.21</v>
       </c>
       <c r="F149" t="s">
         <v>161</v>
@@ -5193,7 +5193,7 @@
         <v>1</v>
       </c>
       <c r="I149">
-        <v>-1825.52</v>
+        <v>1124.21</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -5201,16 +5201,16 @@
         <v>138</v>
       </c>
       <c r="B150">
-        <v>12</v>
+        <v>-48</v>
       </c>
       <c r="C150">
-        <v>78.56440000000001</v>
+        <v>38.0316</v>
       </c>
       <c r="D150">
-        <v>1014.12</v>
+        <v>3230.88</v>
       </c>
       <c r="E150">
-        <v>942.77</v>
+        <v>-1825.52</v>
       </c>
       <c r="F150" t="s">
         <v>161</v>
@@ -5222,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="I150">
-        <v>942.77</v>
+        <v>-1825.52</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -5230,16 +5230,16 @@
         <v>139</v>
       </c>
       <c r="B151">
-        <v>-1200</v>
+        <v>12</v>
       </c>
       <c r="C151">
-        <v>3.9249</v>
+        <v>78.56440000000001</v>
       </c>
       <c r="D151">
-        <v>52320</v>
+        <v>1014.12</v>
       </c>
       <c r="E151">
-        <v>-4709.88</v>
+        <v>942.77</v>
       </c>
       <c r="F151" t="s">
         <v>161</v>
@@ -5251,7 +5251,7 @@
         <v>1</v>
       </c>
       <c r="I151">
-        <v>-4709.88</v>
+        <v>942.77</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -5259,16 +5259,16 @@
         <v>140</v>
       </c>
       <c r="B152">
-        <v>200</v>
+        <v>-1200</v>
       </c>
       <c r="C152">
-        <v>2.9197</v>
+        <v>3.9249</v>
       </c>
       <c r="D152">
-        <v>322</v>
+        <v>52320</v>
       </c>
       <c r="E152">
-        <v>583.9400000000001</v>
+        <v>-4709.88</v>
       </c>
       <c r="F152" t="s">
         <v>161</v>
@@ -5280,7 +5280,7 @@
         <v>1</v>
       </c>
       <c r="I152">
-        <v>583.9400000000001</v>
+        <v>-4709.88</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -5288,16 +5288,16 @@
         <v>141</v>
       </c>
       <c r="B153">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C153">
-        <v>1.9261</v>
+        <v>2.9197</v>
       </c>
       <c r="D153">
-        <v>-3398</v>
+        <v>322</v>
       </c>
       <c r="E153">
-        <v>192.61</v>
+        <v>583.9400000000001</v>
       </c>
       <c r="F153" t="s">
         <v>161</v>
@@ -5309,7 +5309,7 @@
         <v>1</v>
       </c>
       <c r="I153">
-        <v>192.61</v>
+        <v>583.9400000000001</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -5317,16 +5317,16 @@
         <v>142</v>
       </c>
       <c r="B154">
-        <v>-800</v>
+        <v>100</v>
       </c>
       <c r="C154">
-        <v>68.1585</v>
+        <v>1.9261</v>
       </c>
       <c r="D154">
-        <v>-329752</v>
+        <v>-3398</v>
       </c>
       <c r="E154">
-        <v>-54526.8</v>
+        <v>192.61</v>
       </c>
       <c r="F154" t="s">
         <v>161</v>
@@ -5338,7 +5338,7 @@
         <v>1</v>
       </c>
       <c r="I154">
-        <v>-54526.8</v>
+        <v>192.61</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -5346,16 +5346,16 @@
         <v>143</v>
       </c>
       <c r="B155">
-        <v>-500</v>
+        <v>-800</v>
       </c>
       <c r="C155">
-        <v>67.27460000000001</v>
+        <v>68.1585</v>
       </c>
       <c r="D155">
-        <v>-205280</v>
+        <v>-329752</v>
       </c>
       <c r="E155">
-        <v>-33637.3</v>
+        <v>-54526.8</v>
       </c>
       <c r="F155" t="s">
         <v>161</v>
@@ -5367,7 +5367,7 @@
         <v>1</v>
       </c>
       <c r="I155">
-        <v>-33637.3</v>
+        <v>-54526.8</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -5375,16 +5375,16 @@
         <v>144</v>
       </c>
       <c r="B156">
-        <v>1300</v>
+        <v>-500</v>
       </c>
       <c r="C156">
-        <v>44.4473</v>
+        <v>67.27460000000001</v>
       </c>
       <c r="D156">
-        <v>439140</v>
+        <v>-205280</v>
       </c>
       <c r="E156">
-        <v>57781.49</v>
+        <v>-33637.3</v>
       </c>
       <c r="F156" t="s">
         <v>161</v>
@@ -5396,7 +5396,7 @@
         <v>1</v>
       </c>
       <c r="I156">
-        <v>57781.49</v>
+        <v>-33637.3</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -5404,16 +5404,16 @@
         <v>145</v>
       </c>
       <c r="B157">
-        <v>-500</v>
+        <v>1300</v>
       </c>
       <c r="C157">
-        <v>24.6804</v>
+        <v>44.4473</v>
       </c>
       <c r="D157">
-        <v>-125430</v>
+        <v>439140</v>
       </c>
       <c r="E157">
-        <v>-12340.2</v>
+        <v>57781.49</v>
       </c>
       <c r="F157" t="s">
         <v>161</v>
@@ -5425,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="I157">
-        <v>-12340.2</v>
+        <v>57781.49</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -5433,16 +5433,16 @@
         <v>146</v>
       </c>
       <c r="B158">
-        <v>500</v>
+        <v>-500</v>
       </c>
       <c r="C158">
-        <v>9.4194</v>
+        <v>24.6804</v>
       </c>
       <c r="D158">
-        <v>63730</v>
+        <v>-125430</v>
       </c>
       <c r="E158">
-        <v>4709.7</v>
+        <v>-12340.2</v>
       </c>
       <c r="F158" t="s">
         <v>161</v>
@@ -5454,7 +5454,7 @@
         <v>1</v>
       </c>
       <c r="I158">
-        <v>4709.7</v>
+        <v>-12340.2</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -5462,16 +5462,16 @@
         <v>147</v>
       </c>
       <c r="B159">
-        <v>-50</v>
+        <v>500</v>
       </c>
       <c r="C159">
-        <v>18.0986</v>
+        <v>9.4194</v>
       </c>
       <c r="D159">
-        <v>-2567.5</v>
+        <v>63730</v>
       </c>
       <c r="E159">
-        <v>-904.9299999999999</v>
+        <v>4709.7</v>
       </c>
       <c r="F159" t="s">
         <v>161</v>
@@ -5483,7 +5483,7 @@
         <v>1</v>
       </c>
       <c r="I159">
-        <v>-904.9299999999999</v>
+        <v>4709.7</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -5491,16 +5491,16 @@
         <v>148</v>
       </c>
       <c r="B160">
-        <v>-236</v>
+        <v>-50</v>
       </c>
       <c r="C160">
-        <v>19.8483</v>
+        <v>18.0986</v>
       </c>
       <c r="D160">
-        <v>-12798.28</v>
+        <v>-2567.5</v>
       </c>
       <c r="E160">
-        <v>-4684.2</v>
+        <v>-904.9299999999999</v>
       </c>
       <c r="F160" t="s">
         <v>161</v>
@@ -5512,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="I160">
-        <v>-4684.2</v>
+        <v>-904.9299999999999</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -5520,16 +5520,16 @@
         <v>149</v>
       </c>
       <c r="B161">
-        <v>-140</v>
+        <v>-236</v>
       </c>
       <c r="C161">
-        <v>20.7482</v>
+        <v>19.8483</v>
       </c>
       <c r="D161">
-        <v>-7674.8</v>
+        <v>-12798.28</v>
       </c>
       <c r="E161">
-        <v>-2904.75</v>
+        <v>-4684.2</v>
       </c>
       <c r="F161" t="s">
         <v>161</v>
@@ -5541,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="I161">
-        <v>-2904.75</v>
+        <v>-4684.2</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -5549,16 +5549,16 @@
         <v>150</v>
       </c>
       <c r="B162">
-        <v>-48</v>
+        <v>-140</v>
       </c>
       <c r="C162">
-        <v>53.6988</v>
+        <v>20.7482</v>
       </c>
       <c r="D162">
-        <v>-3291.84</v>
+        <v>-7674.8</v>
       </c>
       <c r="E162">
-        <v>-2577.54</v>
+        <v>-2904.75</v>
       </c>
       <c r="F162" t="s">
         <v>161</v>
@@ -5570,7 +5570,7 @@
         <v>1</v>
       </c>
       <c r="I162">
-        <v>-2577.54</v>
+        <v>-2904.75</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -5578,16 +5578,16 @@
         <v>151</v>
       </c>
       <c r="B163">
-        <v>48</v>
+        <v>-48</v>
       </c>
       <c r="C163">
-        <v>31.4831</v>
+        <v>53.6988</v>
       </c>
       <c r="D163">
-        <v>-3151.68</v>
+        <v>-3291.84</v>
       </c>
       <c r="E163">
-        <v>1511.19</v>
+        <v>-2577.54</v>
       </c>
       <c r="F163" t="s">
         <v>161</v>
@@ -5599,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="I163">
-        <v>1511.19</v>
+        <v>-2577.54</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -5607,16 +5607,16 @@
         <v>152</v>
       </c>
       <c r="B164">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C164">
-        <v>26.4873</v>
+        <v>31.4831</v>
       </c>
       <c r="D164">
-        <v>-3951.6</v>
+        <v>-3151.68</v>
       </c>
       <c r="E164">
-        <v>1589.24</v>
+        <v>1511.19</v>
       </c>
       <c r="F164" t="s">
         <v>161</v>
@@ -5628,7 +5628,7 @@
         <v>1</v>
       </c>
       <c r="I164">
-        <v>1589.24</v>
+        <v>1511.19</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -5636,16 +5636,16 @@
         <v>153</v>
       </c>
       <c r="B165">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="C165">
-        <v>21.5247</v>
+        <v>26.4873</v>
       </c>
       <c r="D165">
-        <v>-7066.44</v>
+        <v>-3951.6</v>
       </c>
       <c r="E165">
-        <v>2324.67</v>
+        <v>1589.24</v>
       </c>
       <c r="F165" t="s">
         <v>161</v>
@@ -5657,7 +5657,7 @@
         <v>1</v>
       </c>
       <c r="I165">
-        <v>2324.67</v>
+        <v>1589.24</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -5665,16 +5665,16 @@
         <v>154</v>
       </c>
       <c r="B166">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="C166">
-        <v>8.8141</v>
+        <v>21.5247</v>
       </c>
       <c r="D166">
-        <v>-2714</v>
+        <v>-7066.44</v>
       </c>
       <c r="E166">
-        <v>440.7</v>
+        <v>2324.67</v>
       </c>
       <c r="F166" t="s">
         <v>161</v>
@@ -5686,7 +5686,7 @@
         <v>1</v>
       </c>
       <c r="I166">
-        <v>440.7</v>
+        <v>2324.67</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -5694,16 +5694,16 @@
         <v>155</v>
       </c>
       <c r="B167">
-        <v>-30</v>
+        <v>50</v>
       </c>
       <c r="C167">
-        <v>46.5063</v>
+        <v>8.8141</v>
       </c>
       <c r="D167">
-        <v>5312.1</v>
+        <v>-2714</v>
       </c>
       <c r="E167">
-        <v>-1395.19</v>
+        <v>440.7</v>
       </c>
       <c r="F167" t="s">
         <v>161</v>
@@ -5715,7 +5715,7 @@
         <v>1</v>
       </c>
       <c r="I167">
-        <v>-1395.19</v>
+        <v>440.7</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -5723,16 +5723,16 @@
         <v>156</v>
       </c>
       <c r="B168">
-        <v>10</v>
+        <v>-30</v>
       </c>
       <c r="C168">
-        <v>28.5929</v>
+        <v>46.5063</v>
       </c>
       <c r="D168">
-        <v>1309.9</v>
+        <v>5312.1</v>
       </c>
       <c r="E168">
-        <v>285.93</v>
+        <v>-1395.19</v>
       </c>
       <c r="F168" t="s">
         <v>161</v>
@@ -5744,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="I168">
-        <v>285.93</v>
+        <v>-1395.19</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -5752,25 +5752,28 @@
         <v>157</v>
       </c>
       <c r="B169">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="C169">
-        <v>0.0137</v>
+        <v>28.5929</v>
       </c>
       <c r="D169">
-        <v>-0</v>
+        <v>1309.9</v>
       </c>
       <c r="E169">
-        <v>0.86</v>
+        <v>285.93</v>
       </c>
       <c r="F169" t="s">
         <v>161</v>
       </c>
+      <c r="G169" t="s">
+        <v>166</v>
+      </c>
       <c r="H169">
         <v>1</v>
       </c>
       <c r="I169">
-        <v>0.86</v>
+        <v>285.93</v>
       </c>
     </row>
   </sheetData>
